--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE933B0-DCDA-4800-A61E-FD717CCB97DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207B045C-65DF-4056-AEF0-A1090A7280CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="多语言|Language" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -81,10 +81,6 @@
   </si>
   <si>
     <t>英文</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>##</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -360,6 +356,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -372,7 +369,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="差" xfId="1" builtinId="27"/>
@@ -671,16 +667,16 @@
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="5"/>
       <c r="I1"/>
@@ -714,16 +710,16 @@
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2"/>
@@ -794,16 +790,16 @@
         <v>8</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4"/>
@@ -836,22 +832,20 @@
         <v>9</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
-        <v>11</v>
-      </c>
+      <c r="A6" s="7"/>
       <c r="B6">
         <v>2</v>
       </c>
@@ -859,13 +853,13 @@
         <v>10</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -895,10 +889,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="3"/>
-      <c r="D1" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="10"/>
+      <c r="D1" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="11"/>
       <c r="F1" s="5"/>
       <c r="G1"/>
       <c r="H1"/>
@@ -927,13 +921,13 @@
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="12"/>
+      <c r="D2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="13"/>
       <c r="F2" s="5"/>
       <c r="G2"/>
       <c r="H2"/>
@@ -962,7 +956,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>8</v>
@@ -998,7 +992,7 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B4" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7" t="s">
@@ -1009,51 +1003,49 @@
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>11</v>
-      </c>
+      <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="7" t="s">
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B7" s="9" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B7" s="13" t="s">
+      <c r="D7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="E7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="13" t="s">
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B8" s="9" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B8" s="13" t="s">
+      <c r="D8" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="E8" s="9" t="s">
         <v>39</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1063,5 +1055,6 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207B045C-65DF-4056-AEF0-A1090A7280CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBFCADB-E14B-4019-9630-0BD38E158C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36000" yWindow="1020" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="多语言|Language" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -197,6 +197,18 @@
   </si>
   <si>
     <t>Start</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>next_level_btn</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一关</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Next Level</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -874,7 +886,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2525A7A-E1FA-4A3B-809C-FFEA7B53C7CA}">
-  <dimension ref="A1:AA8"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
@@ -1048,6 +1060,17 @@
         <v>39</v>
       </c>
     </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B9" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D1:E1"/>

--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBFCADB-E14B-4019-9630-0BD38E158C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7CB1A6-3C73-40A9-902D-6EE8837430A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36000" yWindow="1020" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36000" yWindow="1020" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="多语言|Language" sheetId="1" r:id="rId1"/>
@@ -136,10 +136,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>AaFengKuangYuanShiRen</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>float</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -210,6 +206,9 @@
   <si>
     <t>Next Level</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AlimamaFangYuanTiVF</t>
   </si>
 </sst>
 </file>
@@ -688,7 +687,7 @@
         <v>21</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H1" s="5"/>
       <c r="I1"/>
@@ -731,7 +730,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2"/>
@@ -811,7 +810,7 @@
         <v>23</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4"/>
@@ -850,7 +849,7 @@
         <v>19</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -871,7 +870,7 @@
         <v>20</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -880,7 +879,7 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -902,7 +901,7 @@
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E1" s="11"/>
       <c r="F1" s="5"/>
@@ -937,7 +936,7 @@
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="5"/>
@@ -1021,54 +1020,54 @@
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>32</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>38</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B9" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>41</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7CB1A6-3C73-40A9-902D-6EE8837430A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9607CFC7-4A75-4D15-883B-FA334B9A7B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36000" yWindow="1020" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4860" yWindow="2520" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="多语言|Language" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -209,6 +209,18 @@
   </si>
   <si>
     <t>AlimamaFangYuanTiVF</t>
+  </si>
+  <si>
+    <t>level_title</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>第{0}关 - {1}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level {0} - {1}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -885,10 +897,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2525A7A-E1FA-4A3B-809C-FFEA7B53C7CA}">
-  <dimension ref="A1:AA9"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1070,6 +1083,17 @@
         <v>41</v>
       </c>
     </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D1:E1"/>

--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9607CFC7-4A75-4D15-883B-FA334B9A7B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E7814E-FABE-4409-BC60-CC81BC249E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4860" yWindow="2520" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="多语言|Language" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -220,6 +220,66 @@
   </si>
   <si>
     <t>Level {0} - {1}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>setting_title</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SETTING</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>setting_music</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>setting_sfx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>setting_notify</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>setting_language</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音乐</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>通知</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>语言</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MUSIC</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SFX</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOTIFICATION</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LANGUAGE</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -897,7 +957,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2525A7A-E1FA-4A3B-809C-FFEA7B53C7CA}">
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
@@ -1094,6 +1154,61 @@
         <v>45</v>
       </c>
     </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B12" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B15" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D1:E1"/>

--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E7814E-FABE-4409-BC60-CC81BC249E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEF221D-C0AA-44AF-AAA9-7271F01A5E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36000" yWindow="1200" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="多语言|Language" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="76">
   <si>
     <t>##var</t>
   </si>
@@ -280,6 +280,64 @@
   </si>
   <si>
     <t>LANGUAGE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>finish_title</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>胜利</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Victory</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>finish_completeAllTitle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>抱歉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sorry</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>finish_des</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜！你已经通关了这一关！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Congratulations! You’ve beaten this stage!</t>
+  </si>
+  <si>
+    <t>finish_completeDes</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你很厉害，完成了所有关系，请等我们后续更新新的挑战</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>You're awesome, you've completed all the relationships. Please wait for our next update with new challenges.</t>
+  </si>
+  <si>
+    <t>btn_confirm</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>确认</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Confirm</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -957,7 +1015,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2525A7A-E1FA-4A3B-809C-FFEA7B53C7CA}">
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
@@ -1209,6 +1267,61 @@
         <v>60</v>
       </c>
     </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="B16" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B18" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B19" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B20" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D1:E1"/>

--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEF221D-C0AA-44AF-AAA9-7271F01A5E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D399521-A248-4310-8AF1-C03AF14E210A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36000" yWindow="1200" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="多语言|Language" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="101">
   <si>
     <t>##var</t>
   </si>
@@ -338,6 +338,99 @@
   </si>
   <si>
     <t>Confirm</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>getCoin_Title</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取金币</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Get Coins</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>getCoin_Body_unClaim</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>今天的金币已经备好啦，快来领取吧！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Your daily coins are ready, come and claim them!</t>
+  </si>
+  <si>
+    <t>今日金币已领取，明天再来哦～</t>
+  </si>
+  <si>
+    <t>You've claimed today's coins, come back tomorrow~</t>
+  </si>
+  <si>
+    <t>getCoin_Body_claim</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>getCoin_Btn_unClaim</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>领取今日金币</t>
+  </si>
+  <si>
+    <t>getCoin_Btn_claim</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我知道了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Got it</t>
+  </si>
+  <si>
+    <t>getCoin_Share_Body_unClaim</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>getCoin_Share_Body_claim</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>getCoin_Share_Btn_unClaim</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>getCoin_Share_Btn_claim</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>去分享</t>
+  </si>
+  <si>
+    <t>每次分享可获得 {0} 金币，今日剩余 {1} 次</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} coins per share,{1} left today</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>今日分享次数已用完</t>
+  </si>
+  <si>
+    <t>Claim Coins</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>No shares left today</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Share Now</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1015,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2525A7A-E1FA-4A3B-809C-FFEA7B53C7CA}">
-  <dimension ref="A1:AA20"/>
+  <dimension ref="A1:AA29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
@@ -1322,6 +1415,105 @@
         <v>75</v>
       </c>
     </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B22" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B23" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B24" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B25" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B26" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B27" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B28" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B29" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D1:E1"/>

--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D399521-A248-4310-8AF1-C03AF14E210A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CAACB7D-04B0-43E6-BDF2-8F6AB3DBF6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="110">
   <si>
     <t>##var</t>
   </si>
@@ -431,6 +431,41 @@
   </si>
   <si>
     <t>Share Now</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>toast_select</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>请先选择笔画</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>toast_answerFinded</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>该答案已找到</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>toast_answerError</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>所选笔画组合不正确</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Please select a stroke first.</t>
+  </si>
+  <si>
+    <t>The correct answer is found</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>That stroke combination is not valid</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1108,11 +1143,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2525A7A-E1FA-4A3B-809C-FFEA7B53C7CA}">
-  <dimension ref="A1:AA29"/>
+  <dimension ref="A1:AA32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.875" customWidth="1"/>
     <col min="5" max="5" width="18.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1514,6 +1549,39 @@
         <v>89</v>
       </c>
     </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B30" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B31" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B32" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D1:E1"/>

--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CAACB7D-04B0-43E6-BDF2-8F6AB3DBF6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A13522-CA5A-45C9-BFEB-8A00442B00F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="113">
   <si>
     <t>##var</t>
   </si>
@@ -466,6 +466,18 @@
   </si>
   <si>
     <t>That stroke combination is not valid</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>game_des</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>找出{0}个常用字</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Find {0} commonly‑used Chinese characters</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1143,7 +1155,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2525A7A-E1FA-4A3B-809C-FFEA7B53C7CA}">
-  <dimension ref="A1:AA32"/>
+  <dimension ref="A1:AA33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
@@ -1582,6 +1594,17 @@
         <v>109</v>
       </c>
     </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B33" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D1:E1"/>
